--- a/codex/bundles/WebGl_Economy_IntegratedSimulationReadinessBundle_v16/05_spreadsheets/implementation_matrix.xlsx
+++ b/codex/bundles/WebGl_Economy_IntegratedSimulationReadinessBundle_v16/05_spreadsheets/implementation_matrix.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9f423c11912143f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subbundles" sheetId="2" r:id="R35eda081b3174fea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R344443132a26439a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness Probes" sheetId="4" r:id="R9f75c0ed9832493e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5b48b322952f4e55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R672b7a70149d4c2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subbundles" sheetId="2" r:id="Rb2420eb86389455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" r:id="R06b0006a15814559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness Probes" sheetId="4" r:id="Rde00b75c1bef4312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R937a4d7442af4843"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -25,11 +25,16 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -38,7 +43,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1F4E79"/>
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -49,7 +64,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -93,6 +108,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -392,7 +416,7 @@
         <x:v>&lt;= 320 hard, &lt;=220 preferred</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
-        <x:v>Some runtime files are still warning-level</x:v>
+        <x:v>Completed; warnings remain below hard threshold</x:v>
       </x:c>
       <x:c r="G5" s="13"/>
       <x:c r="H5" s="13"/>
@@ -414,7 +438,7 @@
         <x:v>Executable stages</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
-        <x:v>Needs stronger validation and proof</x:v>
+        <x:v>Executable stages validated with strict traceability</x:v>
       </x:c>
       <x:c r="G6" s="13"/>
       <x:c r="H6" s="13"/>
@@ -436,7 +460,7 @@
         <x:v>Reusable builder/analyzer/store</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
-        <x:v>Partly implemented; analysis still too test-local</x:v>
+        <x:v>Reusable builder/analyzer/diff/store completed</x:v>
       </x:c>
       <x:c r="G7" s="13"/>
       <x:c r="H7" s="13"/>
@@ -458,7 +482,7 @@
         <x:v>Backend-neutral</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
-        <x:v>Currently simple-backend oriented</x:v>
+        <x:v>Backend registry and injected backend tests pass</x:v>
       </x:c>
       <x:c r="G8" s="13"/>
       <x:c r="H8" s="13"/>
@@ -511,9 +535,15 @@
         <x:v>Do not create new branch</x:v>
       </x:c>
       <x:c r="C11" s="13"/>
-      <x:c r="D11" s="13"/>
-      <x:c r="E11" s="13"/>
-      <x:c r="F11" s="13"/>
+      <x:c r="D11" s="17" t="str">
+        <x:v>Closure</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="str">
+        <x:v>SB01-SB15 implemented and validated</x:v>
+      </x:c>
       <x:c r="G11" s="13"/>
       <x:c r="H11" s="13"/>
       <x:c r="I11" s="13"/>
@@ -1639,7 +1669,9 @@
       <x:c r="I1" s="12" t="str">
         <x:v>Risk if skipped</x:v>
       </x:c>
-      <x:c r="J1" s="12"/>
+      <x:c r="J1" s="18" t="str">
+        <x:v>Execution status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="13" t="str">
@@ -1669,7 +1701,9 @@
       <x:c r="I2" s="13" t="str">
         <x:v>Implementation can drift or mix repos</x:v>
       </x:c>
-      <x:c r="J2" s="13"/>
+      <x:c r="J2" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="13" t="str">
@@ -1699,7 +1733,9 @@
       <x:c r="I3" s="13" t="str">
         <x:v>Runtime becomes hard to maintain</x:v>
       </x:c>
-      <x:c r="J3" s="13"/>
+      <x:c r="J3" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="13" t="str">
@@ -1729,7 +1765,9 @@
       <x:c r="I4" s="13" t="str">
         <x:v>Actions such as go-use-return break visually</x:v>
       </x:c>
-      <x:c r="J4" s="13"/>
+      <x:c r="J4" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="str">
@@ -1759,7 +1797,9 @@
       <x:c r="I5" s="13" t="str">
         <x:v>Delayed errors disappear after initial call</x:v>
       </x:c>
-      <x:c r="J5" s="13"/>
+      <x:c r="J5" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="str">
@@ -1789,7 +1829,9 @@
       <x:c r="I6" s="13" t="str">
         <x:v>Run document looks valid but cannot execute</x:v>
       </x:c>
-      <x:c r="J6" s="13"/>
+      <x:c r="J6" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="str">
@@ -1819,7 +1861,9 @@
       <x:c r="I7" s="13" t="str">
         <x:v>Bridge becomes unmaintainable</x:v>
       </x:c>
-      <x:c r="J7" s="13"/>
+      <x:c r="J7" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="13" t="str">
@@ -1849,7 +1893,9 @@
       <x:c r="I8" s="13" t="str">
         <x:v>Snapshot exists but cannot support real analysis</x:v>
       </x:c>
-      <x:c r="J8" s="13"/>
+      <x:c r="J8" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="13" t="str">
@@ -1879,7 +1925,9 @@
       <x:c r="I9" s="13" t="str">
         <x:v>Cannot inspect paused runs later</x:v>
       </x:c>
-      <x:c r="J9" s="13"/>
+      <x:c r="J9" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="13" t="str">
@@ -1909,7 +1957,9 @@
       <x:c r="I10" s="13" t="str">
         <x:v>Joined workflow cannot support ledger later</x:v>
       </x:c>
-      <x:c r="J10" s="13"/>
+      <x:c r="J10" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="13" t="str">
@@ -1939,7 +1989,9 @@
       <x:c r="I11" s="13" t="str">
         <x:v>Visualization abstractions become WebGL-specific</x:v>
       </x:c>
-      <x:c r="J11" s="13"/>
+      <x:c r="J11" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="13" t="str">
@@ -1969,7 +2021,9 @@
       <x:c r="I12" s="13" t="str">
         <x:v>Kernel hardcodes shared-well/farmer-land</x:v>
       </x:c>
-      <x:c r="J12" s="13"/>
+      <x:c r="J12" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="13" t="str">
@@ -1999,7 +2053,9 @@
       <x:c r="I13" s="13" t="str">
         <x:v>Demo will drive architecture incorrectly</x:v>
       </x:c>
-      <x:c r="J13" s="13"/>
+      <x:c r="J13" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="13" t="str">
@@ -2029,7 +2085,9 @@
       <x:c r="I14" s="13" t="str">
         <x:v>UI demo masks data/bridge errors</x:v>
       </x:c>
-      <x:c r="J14" s="13"/>
+      <x:c r="J14" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="13" t="str">
@@ -2059,7 +2117,9 @@
       <x:c r="I15" s="13" t="str">
         <x:v>Later demo becomes slow or brittle</x:v>
       </x:c>
-      <x:c r="J15" s="13"/>
+      <x:c r="J15" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="13" t="str">
@@ -2089,7 +2149,9 @@
       <x:c r="I16" s="13" t="str">
         <x:v>Partial work looks complete</x:v>
       </x:c>
-      <x:c r="J16" s="13"/>
+      <x:c r="J16" s="16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="13"/>
@@ -3102,7 +3164,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R309b495377cb447f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R023017b2634c4727"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3138,7 +3200,9 @@
       <x:c r="F1" s="12" t="str">
         <x:v>Validation</x:v>
       </x:c>
-      <x:c r="G1" s="12"/>
+      <x:c r="G1" s="18" t="str">
+        <x:v>Closure status</x:v>
+      </x:c>
       <x:c r="H1" s="12"/>
       <x:c r="I1" s="12"/>
       <x:c r="J1" s="12"/>
@@ -3162,7 +3226,9 @@
       <x:c r="F2" s="13" t="str">
         <x:v>Stage barrier tests</x:v>
       </x:c>
-      <x:c r="G2" s="13"/>
+      <x:c r="G2" s="13" t="str">
+        <x:v>Mitigated by barrier audit</x:v>
+      </x:c>
       <x:c r="H2" s="13"/>
       <x:c r="I2" s="13"/>
       <x:c r="J2" s="13"/>
@@ -3186,7 +3252,9 @@
       <x:c r="F3" s="13" t="str">
         <x:v>runtime audit</x:v>
       </x:c>
-      <x:c r="G3" s="13"/>
+      <x:c r="G3" s="13" t="str">
+        <x:v>Mitigated by runtime audit</x:v>
+      </x:c>
       <x:c r="H3" s="13"/>
       <x:c r="I3" s="13"/>
       <x:c r="J3" s="13"/>
@@ -3210,7 +3278,9 @@
       <x:c r="F4" s="13" t="str">
         <x:v>Bridge validator tests</x:v>
       </x:c>
-      <x:c r="G4" s="13"/>
+      <x:c r="G4" s="13" t="str">
+        <x:v>Mitigated by strict bridge tests</x:v>
+      </x:c>
       <x:c r="H4" s="13"/>
       <x:c r="I4" s="13"/>
       <x:c r="J4" s="13"/>
@@ -3234,7 +3304,9 @@
       <x:c r="F5" s="13" t="str">
         <x:v>Frame action count tests</x:v>
       </x:c>
-      <x:c r="G5" s="13"/>
+      <x:c r="G5" s="13" t="str">
+        <x:v>Mitigated by frame/global action tests</x:v>
+      </x:c>
       <x:c r="H5" s="13"/>
       <x:c r="I5" s="13"/>
       <x:c r="J5" s="13"/>
@@ -3258,7 +3330,9 @@
       <x:c r="F6" s="13" t="str">
         <x:v>Analyzer unit tests</x:v>
       </x:c>
-      <x:c r="G6" s="13"/>
+      <x:c r="G6" s="13" t="str">
+        <x:v>Mitigated by reusable analyzer tests</x:v>
+      </x:c>
       <x:c r="H6" s="13"/>
       <x:c r="I6" s="13"/>
       <x:c r="J6" s="13"/>
@@ -3282,7 +3356,9 @@
       <x:c r="F7" s="13" t="str">
         <x:v>Diff tests</x:v>
       </x:c>
-      <x:c r="G7" s="13"/>
+      <x:c r="G7" s="13" t="str">
+        <x:v>Mitigated by expanded diff tests</x:v>
+      </x:c>
       <x:c r="H7" s="13"/>
       <x:c r="I7" s="13"/>
       <x:c r="J7" s="13"/>
@@ -3306,7 +3382,9 @@
       <x:c r="F8" s="13" t="str">
         <x:v>Injected backend test</x:v>
       </x:c>
-      <x:c r="G8" s="13"/>
+      <x:c r="G8" s="13" t="str">
+        <x:v>Mitigated by backend registry tests</x:v>
+      </x:c>
       <x:c r="H8" s="13"/>
       <x:c r="I8" s="13"/>
       <x:c r="J8" s="13"/>
@@ -3330,7 +3408,9 @@
       <x:c r="F9" s="13" t="str">
         <x:v>Boundary audit</x:v>
       </x:c>
-      <x:c r="G9" s="13"/>
+      <x:c r="G9" s="13" t="str">
+        <x:v>Mitigated by boundary audit</x:v>
+      </x:c>
       <x:c r="H9" s="13"/>
       <x:c r="I9" s="13"/>
       <x:c r="J9" s="13"/>
@@ -3354,7 +3434,9 @@
       <x:c r="F10" s="13" t="str">
         <x:v>Perf probe</x:v>
       </x:c>
-      <x:c r="G10" s="13"/>
+      <x:c r="G10" s="13" t="str">
+        <x:v>Mitigated by performance probe</x:v>
+      </x:c>
       <x:c r="H10" s="13"/>
       <x:c r="I10" s="13"/>
       <x:c r="J10" s="13"/>
@@ -3378,7 +3460,9 @@
       <x:c r="F11" s="13" t="str">
         <x:v>Boundary audit</x:v>
       </x:c>
-      <x:c r="G11" s="13"/>
+      <x:c r="G11" s="13" t="str">
+        <x:v>Mitigated by reference audit</x:v>
+      </x:c>
       <x:c r="H11" s="13"/>
       <x:c r="I11" s="13"/>
       <x:c r="J11" s="13"/>
@@ -4454,7 +4538,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77fa0e4ecf1c4f2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42a17ccb133c4188"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5722,7 +5806,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reae5be6654e043c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec2f375c71ae49ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5755,7 +5839,9 @@
       <x:c r="E1" s="12" t="str">
         <x:v>Blocks</x:v>
       </x:c>
-      <x:c r="F1" s="12"/>
+      <x:c r="F1" s="18" t="str">
+        <x:v>Execution result</x:v>
+      </x:c>
       <x:c r="G1" s="12"/>
       <x:c r="H1" s="12"/>
       <x:c r="I1" s="12"/>
@@ -5777,7 +5863,9 @@
       <x:c r="E2" s="13" t="str">
         <x:v>SB02, SB03</x:v>
       </x:c>
-      <x:c r="F2" s="13"/>
+      <x:c r="F2" s="16" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
       <x:c r="G2" s="13"/>
       <x:c r="H2" s="13"/>
       <x:c r="I2" s="13"/>
@@ -5799,7 +5887,9 @@
       <x:c r="E3" s="13" t="str">
         <x:v>SB03, SB04</x:v>
       </x:c>
-      <x:c r="F3" s="13"/>
+      <x:c r="F3" s="16" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
       <x:c r="G3" s="13"/>
       <x:c r="H3" s="13"/>
       <x:c r="I3" s="13"/>
@@ -5821,7 +5911,9 @@
       <x:c r="E4" s="13" t="str">
         <x:v>All Components work</x:v>
       </x:c>
-      <x:c r="F4" s="13"/>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Covered by focused test/build graph</x:v>
+      </x:c>
       <x:c r="G4" s="13"/>
       <x:c r="H4" s="13"/>
       <x:c r="I4" s="13"/>
@@ -5843,7 +5935,9 @@
       <x:c r="E5" s="13" t="str">
         <x:v>SB05-SB13</x:v>
       </x:c>
-      <x:c r="F5" s="13"/>
+      <x:c r="F5" s="16" t="str">
+        <x:v>Passed via powershell fallback</x:v>
+      </x:c>
       <x:c r="G5" s="13"/>
       <x:c r="H5" s="13"/>
       <x:c r="I5" s="13"/>
@@ -5865,7 +5959,9 @@
       <x:c r="E6" s="13" t="str">
         <x:v>All Economy work</x:v>
       </x:c>
-      <x:c r="F6" s="13"/>
+      <x:c r="F6" s="16" t="str">
+        <x:v>Passed: 514 tests</x:v>
+      </x:c>
       <x:c r="G6" s="13"/>
       <x:c r="H6" s="13"/>
       <x:c r="I6" s="13"/>
@@ -5887,7 +5983,9 @@
       <x:c r="E7" s="13" t="str">
         <x:v>SB07, SB13</x:v>
       </x:c>
-      <x:c r="F7" s="13"/>
+      <x:c r="F7" s="16" t="str">
+        <x:v>Passed through input-pack tests</x:v>
+      </x:c>
       <x:c r="G7" s="13"/>
       <x:c r="H7" s="13"/>
       <x:c r="I7" s="13"/>
@@ -5909,7 +6007,9 @@
       <x:c r="E8" s="13" t="str">
         <x:v>SB13</x:v>
       </x:c>
-      <x:c r="F8" s="13"/>
+      <x:c r="F8" s="16" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
       <x:c r="G8" s="13"/>
       <x:c r="H8" s="13"/>
       <x:c r="I8" s="13"/>
@@ -5931,7 +6031,9 @@
       <x:c r="E9" s="13" t="str">
         <x:v>SB14</x:v>
       </x:c>
-      <x:c r="F9" s="13"/>
+      <x:c r="F9" s="16" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
       <x:c r="G9" s="13"/>
       <x:c r="H9" s="13"/>
       <x:c r="I9" s="13"/>
@@ -7032,7 +7134,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3efc73fb0269428f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15bd694e188b4d10"/>
   </x:tableParts>
 </x:worksheet>
 </file>